--- a/TestFiles/ExcelFiles/RatePerProc.xlsx
+++ b/TestFiles/ExcelFiles/RatePerProc.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>9.42</v>
+        <v>5.36</v>
       </c>
     </row>
   </sheetData>

--- a/TestFiles/ExcelFiles/RatePerProc.xlsx
+++ b/TestFiles/ExcelFiles/RatePerProc.xlsx
@@ -74,7 +74,7 @@
         <v>0</v>
       </c>
       <c r="B1" t="n">
-        <v>7.74</v>
+        <v>2.31</v>
       </c>
     </row>
   </sheetData>
